--- a/data.xlsx
+++ b/data.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plot_Data_Verified" sheetId="1" r:id="R10cd4729b895477b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plot_Data" sheetId="2" r:id="R9d84c56d341d4496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plot_Data_Original" sheetId="3" r:id="Rccfffdd433c54001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plot_Data_Verified" sheetId="1" r:id="R45272ad5ffa74631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plot_Data" sheetId="2" r:id="R2731a4977ee74aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plot_Data_Original" sheetId="3" r:id="Re666c6a6416a4413"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DataTable1" displayName="DataTable1" ref="A1:AF224" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DataTable1" displayName="DataTable1" ref="A1:AF225" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="32">
     <x:tableColumn id="1" name="row_id"/>
     <x:tableColumn id="2" name="T_C"/>
@@ -213,7 +213,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DataTable2" displayName="DataTable2" ref="A1:H247" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DataTable2" displayName="DataTable2" ref="A1:H248" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="row_id"/>
     <x:tableColumn id="2" name="record_equivalence_id"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DataTable3" displayName="DataTable3" ref="A1:C247" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DataTable3" displayName="DataTable3" ref="A1:C248" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="row_id"/>
     <x:tableColumn id="2" name="Nf_cycles"/>
@@ -22035,38 +22035,100 @@
       </x:c>
     </x:row>
     <x:row r="225" ht="25" customHeight="1">
-      <x:c r="A225" s="12"/>
-      <x:c r="B225" s="12"/>
-      <x:c r="C225" s="14"/>
-      <x:c r="D225" s="16"/>
-      <x:c r="E225" s="16"/>
-      <x:c r="F225" s="16"/>
-      <x:c r="G225" s="18"/>
-      <x:c r="H225" s="12"/>
-      <x:c r="I225" s="21"/>
-      <x:c r="J225" s="20"/>
-      <x:c r="K225" s="20"/>
-      <x:c r="L225" s="20"/>
-      <x:c r="M225" s="20"/>
-      <x:c r="N225" s="21"/>
+      <x:c r="A225" s="12" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B225" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C225" s="14" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="D225" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E225" s="16" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F225" s="16" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="G225" s="18" t="n">
+        <x:v>0.628</x:v>
+      </x:c>
+      <x:c r="H225" s="12" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="I225" s="19" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J225" s="20" t="str">
+        <x:v>2D_woven</x:v>
+      </x:c>
+      <x:c r="K225" s="20" t="str">
+        <x:v>2D</x:v>
+      </x:c>
+      <x:c r="L225" s="20" t="str">
+        <x:v>air_or_oxygen</x:v>
+      </x:c>
+      <x:c r="M225" s="20" t="str">
+        <x:v>RT/T&lt;=80</x:v>
+      </x:c>
+      <x:c r="N225" s="19" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="O225" s="12"/>
-      <x:c r="P225" s="20"/>
-      <x:c r="Q225" s="20"/>
-      <x:c r="R225" s="12"/>
-      <x:c r="S225" s="12"/>
-      <x:c r="T225" s="20"/>
-      <x:c r="U225" s="12"/>
-      <x:c r="V225" s="12"/>
-      <x:c r="W225" s="20"/>
-      <x:c r="X225" s="20"/>
-      <x:c r="Y225" s="20"/>
-      <x:c r="Z225" s="20"/>
-      <x:c r="AA225" s="20"/>
-      <x:c r="AB225" s="20"/>
-      <x:c r="AC225" s="20"/>
-      <x:c r="AD225" s="20"/>
-      <x:c r="AE225" s="20"/>
-      <x:c r="AF225" s="20"/>
+      <x:c r="P225" s="20" t="str">
+        <x:v>EQ-R315</x:v>
+      </x:c>
+      <x:c r="Q225" s="20" t="str">
+        <x:v>right_censored_likelihood_training</x:v>
+      </x:c>
+      <x:c r="R225" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S225" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T225" s="20" t="str">
+        <x:v>right_censored</x:v>
+      </x:c>
+      <x:c r="U225" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V225" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W225" s="20" t="str">
+        <x:v>primary_experiment</x:v>
+      </x:c>
+      <x:c r="X225" s="20" t="str">
+        <x:v>primary_table_secondary_UTS_reference</x:v>
+      </x:c>
+      <x:c r="Y225" s="20" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="Z225" s="20" t="str">
+        <x:v>no_confirmed_duplicate</x:v>
+      </x:c>
+      <x:c r="AA225" s="20" t="str">
+        <x:v>&gt;1000000</x:v>
+      </x:c>
+      <x:c r="AB225" s="20" t="str">
+        <x:v>CAMPAIGN-MIN-2D-CSIC-RT</x:v>
+      </x:c>
+      <x:c r="AC225" s="20" t="str">
+        <x:v>J. B. Min | 2013 | Micromechanics Fatigue Damage Analysis Modeling for Fabric Reinforced Ceramic Matrix Composites</x:v>
+      </x:c>
+      <x:c r="AD225" s="20" t="str">
+        <x:v>https://ntrs.nasa.gov/citations/20130014831; Li2016 doi:10.1007/s10443-016-9492-5</x:v>
+      </x:c>
+      <x:c r="AE225" s="20" t="str">
+        <x:v>NASA/TM-2013-217870, Table 5 p.17, row 05: 314 MPa, &gt;1,000,000 cycles; 23 C, R=0.1, 5 Hz. Recorded as right-censored at 1,000,000 cycles. UTS 500 MPa follows the same Li2016 normalization reference as the other Min records.</x:v>
+      </x:c>
+      <x:c r="AF225" s="20" t="str">
+        <x:v>Li2016 PDF p10 / journal p922, section4.1.1 explicitly reports500MPa. Retain as Li reported normalization reference, not a newly verified original experimental mean.</x:v>
+      </x:c>
     </x:row>
     <x:row r="226" ht="25" customHeight="1">
       <x:c r="A226" s="12"/>
@@ -22241,7 +22303,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b9f9068c38c4489"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb21bc02149ab4170"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28683,14 +28745,30 @@
       </x:c>
     </x:row>
     <x:row r="248" ht="25" customHeight="1">
-      <x:c r="A248" s="12"/>
-      <x:c r="B248" s="20"/>
-      <x:c r="C248" s="21"/>
-      <x:c r="D248" s="20"/>
-      <x:c r="E248" s="20"/>
-      <x:c r="F248" s="20"/>
-      <x:c r="G248" s="20"/>
-      <x:c r="H248" s="20"/>
+      <x:c r="A248" s="12" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B248" s="20" t="str">
+        <x:v>EQ-R315</x:v>
+      </x:c>
+      <x:c r="C248" s="19" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D248" s="20" t="str">
+        <x:v>primary_experiment</x:v>
+      </x:c>
+      <x:c r="E248" s="20" t="str">
+        <x:v>primary_table_secondary_UTS_reference</x:v>
+      </x:c>
+      <x:c r="F248" s="20" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G248" s="20" t="str">
+        <x:v>no_confirmed_duplicate</x:v>
+      </x:c>
+      <x:c r="H248" s="20" t="str">
+        <x:v>J. B. Min | 2013 | Micromechanics Fatigue Damage Analysis Modeling for Fabric Reinforced Ceramic Matrix Composites</x:v>
+      </x:c>
     </x:row>
     <x:row r="249" ht="25" customHeight="1">
       <x:c r="A249" s="12"/>
@@ -28745,7 +28823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ea703bc76049ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R339cabcb27b64513"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31477,9 +31555,15 @@
       </x:c>
     </x:row>
     <x:row r="248" ht="25" customHeight="1">
-      <x:c r="A248" s="12"/>
-      <x:c r="B248" s="12"/>
-      <x:c r="C248" s="21"/>
+      <x:c r="A248" s="12" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B248" s="12" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="C248" s="19" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="249" ht="25" customHeight="1">
       <x:c r="A249" s="12"/>
@@ -31509,7 +31593,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb919099e52fa48a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cf19783ff544315"/>
   </x:tableParts>
 </x:worksheet>
 </file>